--- a/output/tables/table_variable_summary_LASSO.xlsx
+++ b/output/tables/table_variable_summary_LASSO.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Feb 1994</t>
   </si>
   <si>
-    <t xml:space="preserve">Sept 2025</t>
+    <t xml:space="preserve">Aug 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Monthly</t>
@@ -341,6 +341,9 @@
     <t xml:space="preserve">sq_error</t>
   </si>
   <si>
+    <t xml:space="preserve">Mar 2016</t>
+  </si>
+  <si>
     <t xml:space="preserve">Apr 2016</t>
   </si>
   <si>
@@ -675,9 +678,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jul 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aug 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Coefficient</t>
@@ -1135,7 +1135,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -1727,10 +1727,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.103</v>
+        <v>-0.095</v>
       </c>
       <c r="C3" t="n">
-        <v>4.079</v>
+        <v>4.081</v>
       </c>
       <c r="D3" t="n">
         <v>-17.3</v>
@@ -1739,7 +1739,7 @@
         <v>11.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1853,10 +1853,10 @@
         <v>0.006</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="E9" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="F9" t="n">
         <v>0.004</v>
@@ -1887,19 +1887,19 @@
         <v>37</v>
       </c>
       <c r="B11" t="n">
-        <v>-139.961</v>
+        <v>-139.995</v>
       </c>
       <c r="C11" t="n">
-        <v>5733.056</v>
+        <v>5957.35</v>
       </c>
       <c r="D11" t="n">
-        <v>-27855</v>
+        <v>-31853</v>
       </c>
       <c r="E11" t="n">
-        <v>72642</v>
+        <v>76228</v>
       </c>
       <c r="F11" t="n">
-        <v>-252</v>
+        <v>-358</v>
       </c>
     </row>
     <row r="12">
@@ -1959,7 +1959,7 @@
         <v>0.615</v>
       </c>
       <c r="F14" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="15">
@@ -2039,7 +2039,7 @@
         <v>0.215</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="19">
@@ -2070,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="D20" t="n">
         <v>-1.297</v>
@@ -2079,7 +2079,7 @@
         <v>1.71</v>
       </c>
       <c r="F20" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="21">
@@ -2087,10 +2087,10 @@
         <v>57</v>
       </c>
       <c r="B21" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="C21" t="n">
-        <v>0.871</v>
+        <v>0.872</v>
       </c>
       <c r="D21" t="n">
         <v>-3.176</v>
@@ -2099,7 +2099,7 @@
         <v>6.858</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.049</v>
+        <v>-0.045</v>
       </c>
     </row>
     <row r="22">
@@ -2150,7 +2150,7 @@
         <v>0.002</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="D24" t="n">
         <v>-0.063</v>
@@ -2187,19 +2187,19 @@
         <v>67</v>
       </c>
       <c r="B26" t="n">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="C26" t="n">
-        <v>0.989</v>
+        <v>0.984</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.127</v>
+        <v>-1.134</v>
       </c>
       <c r="E26" t="n">
-        <v>7.798</v>
+        <v>7.748</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.204</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="27">
@@ -2207,10 +2207,10 @@
         <v>70</v>
       </c>
       <c r="B27" t="n">
-        <v>2.549</v>
+        <v>2.548</v>
       </c>
       <c r="C27" t="n">
-        <v>1.586</v>
+        <v>1.588</v>
       </c>
       <c r="D27" t="n">
         <v>-1.959</v>
@@ -2219,7 +2219,7 @@
         <v>8.999</v>
       </c>
       <c r="F27" t="n">
-        <v>2.426</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="28">
@@ -2230,7 +2230,7 @@
         <v>0.006</v>
       </c>
       <c r="C28" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="D28" t="n">
         <v>-0.208</v>
@@ -2239,7 +2239,7 @@
         <v>0.177</v>
       </c>
       <c r="F28" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="29">
@@ -2307,19 +2307,19 @@
         <v>91</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8457</v>
+        <v>1.8523</v>
       </c>
       <c r="D2" t="n">
         <v>1.0576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9949</v>
+        <v>0.9976</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2352</v>
+        <v>1.2389</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3861</v>
+        <v>0.3867</v>
       </c>
     </row>
     <row r="3">
@@ -2330,19 +2330,19 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>2.14</v>
+        <v>2.1554</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3654</v>
+        <v>0.3679</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8492</v>
+        <v>0.8303</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4111</v>
+        <v>1.4266</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4422</v>
+        <v>0.4487</v>
       </c>
     </row>
     <row r="4">
@@ -2353,19 +2353,19 @@
         <v>93</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0341</v>
+        <v>1.9944</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5908</v>
+        <v>0.5603</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6959</v>
+        <v>0.5683</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3503</v>
+        <v>1.3605</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4212</v>
+        <v>0.4293</v>
       </c>
     </row>
     <row r="5">
@@ -2376,19 +2376,19 @@
         <v>91</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2951</v>
+        <v>0.2963</v>
       </c>
       <c r="D5" t="n">
         <v>0.3071</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4818</v>
+        <v>0.4843</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2099</v>
+        <v>0.2102</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0943</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="6">
@@ -2399,19 +2399,19 @@
         <v>92</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7717</v>
+        <v>1.7972</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2285</v>
+        <v>0.2309</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4616</v>
+        <v>0.4901</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9811</v>
+        <v>0.9983</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2709</v>
+        <v>0.2758</v>
       </c>
     </row>
     <row r="7">
@@ -2422,19 +2422,19 @@
         <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5263</v>
+        <v>1.5341</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3578</v>
+        <v>0.3646</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3476</v>
+        <v>0.3652</v>
       </c>
       <c r="F7" t="n">
-        <v>0.804</v>
+        <v>0.7918</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2069</v>
+        <v>0.2019</v>
       </c>
     </row>
     <row r="8">
@@ -2445,19 +2445,19 @@
         <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>2.171</v>
+        <v>2.1788</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3133</v>
+        <v>0.3132</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1155</v>
+        <v>1.1127</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3524</v>
+        <v>1.3573</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4056</v>
+        <v>0.4067</v>
       </c>
     </row>
   </sheetData>
@@ -2493,7 +2493,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0524</v>
+        <v>1.0379</v>
       </c>
     </row>
     <row r="3">
@@ -2504,7 +2504,7 @@
         <v>49</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1098</v>
+        <v>0.1102</v>
       </c>
     </row>
     <row r="4">
@@ -2515,7 +2515,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0387</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="5">
@@ -2526,7 +2526,7 @@
         <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0354</v>
+        <v>0.0344</v>
       </c>
     </row>
     <row r="6">
@@ -2537,7 +2537,7 @@
         <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0242</v>
+        <v>0.0262</v>
       </c>
     </row>
     <row r="7">
@@ -2548,7 +2548,7 @@
         <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0217</v>
+        <v>0.0224</v>
       </c>
     </row>
     <row r="8">
@@ -2556,10 +2556,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0182</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="9">
@@ -2567,10 +2567,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0177</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="10">
@@ -2581,7 +2581,7 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0104</v>
+        <v>0.0099</v>
       </c>
     </row>
     <row r="11">
@@ -2603,7 +2603,7 @@
         <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0009</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="13">
@@ -2611,7 +2611,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -2688,7 +2688,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2721,7 +2721,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2787,7 +2787,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2832,19 +2832,19 @@
         <v>107</v>
       </c>
       <c r="B2" t="n">
-        <v>1.173</v>
+        <v>0.892</v>
       </c>
       <c r="C2" t="n">
-        <v>1.148</v>
+        <v>1.059</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.025</v>
+        <v>0.167</v>
       </c>
       <c r="E2" t="n">
-        <v>0.025</v>
+        <v>0.167</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0006</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="3">
@@ -2852,19 +2852,19 @@
         <v>108</v>
       </c>
       <c r="B3" t="n">
-        <v>1.078</v>
+        <v>1.173</v>
       </c>
       <c r="C3" t="n">
-        <v>1.466</v>
+        <v>1.152</v>
       </c>
       <c r="D3" t="n">
-        <v>0.387</v>
+        <v>-0.021</v>
       </c>
       <c r="E3" t="n">
-        <v>0.387</v>
+        <v>0.021</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1499</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="4">
@@ -2872,19 +2872,19 @@
         <v>109</v>
       </c>
       <c r="B4" t="n">
-        <v>1.079</v>
+        <v>1.078</v>
       </c>
       <c r="C4" t="n">
-        <v>1.397</v>
+        <v>1.468</v>
       </c>
       <c r="D4" t="n">
-        <v>0.318</v>
+        <v>0.389</v>
       </c>
       <c r="E4" t="n">
-        <v>0.318</v>
+        <v>0.389</v>
       </c>
       <c r="F4" t="n">
-        <v>0.101</v>
+        <v>0.1516</v>
       </c>
     </row>
     <row r="5">
@@ -2892,19 +2892,19 @@
         <v>110</v>
       </c>
       <c r="B5" t="n">
-        <v>0.868</v>
+        <v>1.079</v>
       </c>
       <c r="C5" t="n">
-        <v>1.148</v>
+        <v>1.396</v>
       </c>
       <c r="D5" t="n">
-        <v>0.28</v>
+        <v>0.317</v>
       </c>
       <c r="E5" t="n">
-        <v>0.28</v>
+        <v>0.317</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0783</v>
+        <v>0.1004</v>
       </c>
     </row>
     <row r="6">
@@ -2912,19 +2912,19 @@
         <v>111</v>
       </c>
       <c r="B6" t="n">
-        <v>1.055</v>
+        <v>0.868</v>
       </c>
       <c r="C6" t="n">
-        <v>0.896</v>
+        <v>1.148</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.159</v>
+        <v>0.279</v>
       </c>
       <c r="E6" t="n">
-        <v>0.159</v>
+        <v>0.279</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0254</v>
+        <v>0.0781</v>
       </c>
     </row>
     <row r="7">
@@ -2932,19 +2932,19 @@
         <v>112</v>
       </c>
       <c r="B7" t="n">
-        <v>1.549</v>
+        <v>1.055</v>
       </c>
       <c r="C7" t="n">
-        <v>1.16</v>
+        <v>0.899</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.388</v>
+        <v>-0.157</v>
       </c>
       <c r="E7" t="n">
-        <v>0.388</v>
+        <v>0.157</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1507</v>
+        <v>0.0246</v>
       </c>
     </row>
     <row r="8">
@@ -2952,19 +2952,19 @@
         <v>113</v>
       </c>
       <c r="B8" t="n">
-        <v>1.686</v>
+        <v>1.549</v>
       </c>
       <c r="C8" t="n">
-        <v>1.675</v>
+        <v>1.162</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-0.387</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>0.387</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001</v>
+        <v>0.1499</v>
       </c>
     </row>
     <row r="9">
@@ -2972,19 +2972,19 @@
         <v>114</v>
       </c>
       <c r="B9" t="n">
-        <v>1.684</v>
+        <v>1.686</v>
       </c>
       <c r="C9" t="n">
-        <v>1.678</v>
+        <v>1.675</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.007</v>
+        <v>-0.011</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="10">
@@ -2992,19 +2992,19 @@
         <v>115</v>
       </c>
       <c r="B10" t="n">
-        <v>2.051</v>
+        <v>1.684</v>
       </c>
       <c r="C10" t="n">
-        <v>1.949</v>
+        <v>1.676</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.102</v>
+        <v>-0.008</v>
       </c>
       <c r="E10" t="n">
-        <v>0.102</v>
+        <v>0.008</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0104</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="11">
@@ -3012,19 +3012,19 @@
         <v>116</v>
       </c>
       <c r="B11" t="n">
-        <v>2.51</v>
+        <v>2.051</v>
       </c>
       <c r="C11" t="n">
-        <v>2.271</v>
+        <v>1.954</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.239</v>
+        <v>-0.097</v>
       </c>
       <c r="E11" t="n">
-        <v>0.239</v>
+        <v>0.097</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0571</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="12">
@@ -3032,19 +3032,19 @@
         <v>117</v>
       </c>
       <c r="B12" t="n">
-        <v>2.81</v>
+        <v>2.51</v>
       </c>
       <c r="C12" t="n">
-        <v>2.529</v>
+        <v>2.272</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.281</v>
+        <v>-0.238</v>
       </c>
       <c r="E12" t="n">
-        <v>0.281</v>
+        <v>0.238</v>
       </c>
       <c r="F12" t="n">
-        <v>0.079</v>
+        <v>0.0567</v>
       </c>
     </row>
     <row r="13">
@@ -3052,19 +3052,19 @@
         <v>118</v>
       </c>
       <c r="B13" t="n">
-        <v>2.441</v>
+        <v>2.81</v>
       </c>
       <c r="C13" t="n">
-        <v>2.713</v>
+        <v>2.53</v>
       </c>
       <c r="D13" t="n">
-        <v>0.272</v>
+        <v>-0.28</v>
       </c>
       <c r="E13" t="n">
-        <v>0.272</v>
+        <v>0.28</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0739</v>
+        <v>0.0785</v>
       </c>
     </row>
     <row r="14">
@@ -3072,19 +3072,19 @@
         <v>119</v>
       </c>
       <c r="B14" t="n">
-        <v>2.176</v>
+        <v>2.441</v>
       </c>
       <c r="C14" t="n">
-        <v>2.558</v>
+        <v>2.713</v>
       </c>
       <c r="D14" t="n">
-        <v>0.382</v>
+        <v>0.272</v>
       </c>
       <c r="E14" t="n">
-        <v>0.382</v>
+        <v>0.272</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1461</v>
+        <v>0.0738</v>
       </c>
     </row>
     <row r="15">
@@ -3092,19 +3092,19 @@
         <v>120</v>
       </c>
       <c r="B15" t="n">
-        <v>1.856</v>
+        <v>2.176</v>
       </c>
       <c r="C15" t="n">
-        <v>2.115</v>
+        <v>2.562</v>
       </c>
       <c r="D15" t="n">
-        <v>0.258</v>
+        <v>0.386</v>
       </c>
       <c r="E15" t="n">
-        <v>0.258</v>
+        <v>0.386</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0667</v>
+        <v>0.1489</v>
       </c>
     </row>
     <row r="16">
@@ -3112,19 +3112,19 @@
         <v>121</v>
       </c>
       <c r="B16" t="n">
-        <v>1.641</v>
+        <v>1.856</v>
       </c>
       <c r="C16" t="n">
-        <v>1.889</v>
+        <v>2.117</v>
       </c>
       <c r="D16" t="n">
-        <v>0.248</v>
+        <v>0.26</v>
       </c>
       <c r="E16" t="n">
-        <v>0.248</v>
+        <v>0.26</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0615</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="17">
@@ -3132,19 +3132,19 @@
         <v>122</v>
       </c>
       <c r="B17" t="n">
-        <v>1.725</v>
+        <v>1.641</v>
       </c>
       <c r="C17" t="n">
-        <v>1.666</v>
+        <v>1.887</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.059</v>
+        <v>0.247</v>
       </c>
       <c r="E17" t="n">
-        <v>0.059</v>
+        <v>0.247</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0034</v>
+        <v>0.0608</v>
       </c>
     </row>
     <row r="18">
@@ -3152,19 +3152,19 @@
         <v>123</v>
       </c>
       <c r="B18" t="n">
-        <v>1.928</v>
+        <v>1.725</v>
       </c>
       <c r="C18" t="n">
-        <v>1.802</v>
+        <v>1.672</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.126</v>
+        <v>-0.053</v>
       </c>
       <c r="E18" t="n">
-        <v>0.126</v>
+        <v>0.053</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0158</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="19">
@@ -3172,19 +3172,19 @@
         <v>124</v>
       </c>
       <c r="B19" t="n">
-        <v>2.181</v>
+        <v>1.928</v>
       </c>
       <c r="C19" t="n">
-        <v>2.111</v>
+        <v>1.802</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.07</v>
+        <v>-0.126</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07</v>
+        <v>0.126</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0048</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="20">
@@ -3192,19 +3192,19 @@
         <v>125</v>
       </c>
       <c r="B20" t="n">
-        <v>2.021</v>
+        <v>2.181</v>
       </c>
       <c r="C20" t="n">
-        <v>2.196</v>
+        <v>2.113</v>
       </c>
       <c r="D20" t="n">
-        <v>0.175</v>
+        <v>-0.068</v>
       </c>
       <c r="E20" t="n">
-        <v>0.175</v>
+        <v>0.068</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0306</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="21">
@@ -3212,19 +3212,19 @@
         <v>126</v>
       </c>
       <c r="B21" t="n">
-        <v>2.172</v>
+        <v>2.021</v>
       </c>
       <c r="C21" t="n">
-        <v>2.219</v>
+        <v>2.196</v>
       </c>
       <c r="D21" t="n">
-        <v>0.046</v>
+        <v>0.175</v>
       </c>
       <c r="E21" t="n">
-        <v>0.046</v>
+        <v>0.175</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0022</v>
+        <v>0.0306</v>
       </c>
     </row>
     <row r="22">
@@ -3232,19 +3232,19 @@
         <v>127</v>
       </c>
       <c r="B22" t="n">
-        <v>2.13</v>
+        <v>2.172</v>
       </c>
       <c r="C22" t="n">
-        <v>2.254</v>
+        <v>2.219</v>
       </c>
       <c r="D22" t="n">
-        <v>0.124</v>
+        <v>0.046</v>
       </c>
       <c r="E22" t="n">
-        <v>0.124</v>
+        <v>0.046</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0154</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="23">
@@ -3252,19 +3252,19 @@
         <v>128</v>
       </c>
       <c r="B23" t="n">
-        <v>2.151</v>
+        <v>2.13</v>
       </c>
       <c r="C23" t="n">
-        <v>2.302</v>
+        <v>2.253</v>
       </c>
       <c r="D23" t="n">
-        <v>0.15</v>
+        <v>0.123</v>
       </c>
       <c r="E23" t="n">
-        <v>0.15</v>
+        <v>0.123</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0226</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="24">
@@ -3272,19 +3272,19 @@
         <v>129</v>
       </c>
       <c r="B24" t="n">
-        <v>2.263</v>
+        <v>2.151</v>
       </c>
       <c r="C24" t="n">
-        <v>2.209</v>
+        <v>2.303</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.055</v>
+        <v>0.152</v>
       </c>
       <c r="E24" t="n">
-        <v>0.055</v>
+        <v>0.152</v>
       </c>
       <c r="F24" t="n">
-        <v>0.003</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="25">
@@ -3292,19 +3292,19 @@
         <v>130</v>
       </c>
       <c r="B25" t="n">
-        <v>2.331</v>
+        <v>2.263</v>
       </c>
       <c r="C25" t="n">
-        <v>2.186</v>
+        <v>2.21</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.145</v>
+        <v>-0.054</v>
       </c>
       <c r="E25" t="n">
-        <v>0.145</v>
+        <v>0.054</v>
       </c>
       <c r="F25" t="n">
-        <v>0.021</v>
+        <v>0.0029</v>
       </c>
     </row>
     <row r="26">
@@ -3312,19 +3312,19 @@
         <v>131</v>
       </c>
       <c r="B26" t="n">
-        <v>2.471</v>
+        <v>2.331</v>
       </c>
       <c r="C26" t="n">
-        <v>2.481</v>
+        <v>2.189</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01</v>
+        <v>-0.142</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01</v>
+        <v>0.142</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0001</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="27">
@@ -3332,19 +3332,19 @@
         <v>132</v>
       </c>
       <c r="B27" t="n">
-        <v>2.782</v>
+        <v>2.471</v>
       </c>
       <c r="C27" t="n">
-        <v>2.66</v>
+        <v>2.485</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.122</v>
+        <v>0.014</v>
       </c>
       <c r="E27" t="n">
-        <v>0.122</v>
+        <v>0.014</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0148</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="28">
@@ -3352,19 +3352,19 @@
         <v>133</v>
       </c>
       <c r="B28" t="n">
-        <v>2.808</v>
+        <v>2.782</v>
       </c>
       <c r="C28" t="n">
-        <v>2.778</v>
+        <v>2.662</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.029</v>
+        <v>-0.12</v>
       </c>
       <c r="E28" t="n">
-        <v>0.029</v>
+        <v>0.12</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0009</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="29">
@@ -3372,19 +3372,19 @@
         <v>134</v>
       </c>
       <c r="B29" t="n">
-        <v>2.854</v>
+        <v>2.808</v>
       </c>
       <c r="C29" t="n">
-        <v>2.821</v>
+        <v>2.778</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.033</v>
+        <v>-0.03</v>
       </c>
       <c r="E29" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0011</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="30">
@@ -3392,19 +3392,19 @@
         <v>135</v>
       </c>
       <c r="B30" t="n">
-        <v>2.643</v>
+        <v>2.854</v>
       </c>
       <c r="C30" t="n">
-        <v>2.74</v>
+        <v>2.821</v>
       </c>
       <c r="D30" t="n">
-        <v>0.097</v>
+        <v>-0.033</v>
       </c>
       <c r="E30" t="n">
-        <v>0.097</v>
+        <v>0.033</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0093</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="31">
@@ -3412,19 +3412,19 @@
         <v>136</v>
       </c>
       <c r="B31" t="n">
-        <v>2.332</v>
+        <v>2.643</v>
       </c>
       <c r="C31" t="n">
-        <v>2.555</v>
+        <v>2.741</v>
       </c>
       <c r="D31" t="n">
-        <v>0.223</v>
+        <v>0.098</v>
       </c>
       <c r="E31" t="n">
-        <v>0.223</v>
+        <v>0.098</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0498</v>
+        <v>0.0096</v>
       </c>
     </row>
     <row r="32">
@@ -3432,19 +3432,19 @@
         <v>137</v>
       </c>
       <c r="B32" t="n">
-        <v>2.492</v>
+        <v>2.332</v>
       </c>
       <c r="C32" t="n">
-        <v>2.421</v>
+        <v>2.557</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.071</v>
+        <v>0.225</v>
       </c>
       <c r="E32" t="n">
-        <v>0.071</v>
+        <v>0.225</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0051</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="33">
@@ -3452,19 +3452,19 @@
         <v>138</v>
       </c>
       <c r="B33" t="n">
-        <v>2.147</v>
+        <v>2.492</v>
       </c>
       <c r="C33" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="D33" t="n">
-        <v>0.063</v>
+        <v>-0.072</v>
       </c>
       <c r="E33" t="n">
-        <v>0.063</v>
+        <v>0.072</v>
       </c>
       <c r="F33" t="n">
-        <v>0.004</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="34">
@@ -3472,19 +3472,19 @@
         <v>139</v>
       </c>
       <c r="B34" t="n">
-        <v>2.002</v>
+        <v>2.147</v>
       </c>
       <c r="C34" t="n">
-        <v>1.867</v>
+        <v>2.21</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.135</v>
+        <v>0.063</v>
       </c>
       <c r="E34" t="n">
-        <v>0.135</v>
+        <v>0.063</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0183</v>
+        <v>0.0039</v>
       </c>
     </row>
     <row r="35">
@@ -3492,19 +3492,19 @@
         <v>140</v>
       </c>
       <c r="B35" t="n">
-        <v>1.488</v>
+        <v>2.002</v>
       </c>
       <c r="C35" t="n">
-        <v>1.849</v>
+        <v>1.866</v>
       </c>
       <c r="D35" t="n">
-        <v>0.361</v>
+        <v>-0.136</v>
       </c>
       <c r="E35" t="n">
-        <v>0.361</v>
+        <v>0.136</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1306</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="36">
@@ -3512,19 +3512,19 @@
         <v>141</v>
       </c>
       <c r="B36" t="n">
-        <v>1.519</v>
+        <v>1.488</v>
       </c>
       <c r="C36" t="n">
-        <v>1.56</v>
+        <v>1.853</v>
       </c>
       <c r="D36" t="n">
-        <v>0.041</v>
+        <v>0.365</v>
       </c>
       <c r="E36" t="n">
-        <v>0.041</v>
+        <v>0.365</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0017</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="37">
@@ -3532,19 +3532,19 @@
         <v>142</v>
       </c>
       <c r="B37" t="n">
-        <v>1.883</v>
+        <v>1.519</v>
       </c>
       <c r="C37" t="n">
-        <v>1.805</v>
+        <v>1.562</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.079</v>
+        <v>0.043</v>
       </c>
       <c r="E37" t="n">
-        <v>0.079</v>
+        <v>0.043</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0062</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="38">
@@ -3552,19 +3552,19 @@
         <v>143</v>
       </c>
       <c r="B38" t="n">
-        <v>2.001</v>
+        <v>1.883</v>
       </c>
       <c r="C38" t="n">
-        <v>2.065</v>
+        <v>1.808</v>
       </c>
       <c r="D38" t="n">
-        <v>0.065</v>
+        <v>-0.075</v>
       </c>
       <c r="E38" t="n">
-        <v>0.065</v>
+        <v>0.075</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0042</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="39">
@@ -3572,19 +3572,19 @@
         <v>144</v>
       </c>
       <c r="B39" t="n">
-        <v>1.796</v>
+        <v>2.001</v>
       </c>
       <c r="C39" t="n">
-        <v>1.938</v>
+        <v>2.069</v>
       </c>
       <c r="D39" t="n">
-        <v>0.142</v>
+        <v>0.069</v>
       </c>
       <c r="E39" t="n">
-        <v>0.142</v>
+        <v>0.069</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0201</v>
+        <v>0.0047</v>
       </c>
     </row>
     <row r="40">
@@ -3592,19 +3592,19 @@
         <v>145</v>
       </c>
       <c r="B40" t="n">
-        <v>1.671</v>
+        <v>1.796</v>
       </c>
       <c r="C40" t="n">
-        <v>1.664</v>
+        <v>1.936</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.007</v>
+        <v>0.14</v>
       </c>
       <c r="E40" t="n">
-        <v>0.007</v>
+        <v>0.14</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0001</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="41">
@@ -3612,19 +3612,19 @@
         <v>146</v>
       </c>
       <c r="B41" t="n">
-        <v>1.826</v>
+        <v>1.671</v>
       </c>
       <c r="C41" t="n">
-        <v>1.764</v>
+        <v>1.665</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.063</v>
+        <v>-0.006</v>
       </c>
       <c r="E41" t="n">
-        <v>0.063</v>
+        <v>0.006</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3632,19 +3632,19 @@
         <v>147</v>
       </c>
       <c r="B42" t="n">
-        <v>1.738</v>
+        <v>1.826</v>
       </c>
       <c r="C42" t="n">
-        <v>1.728</v>
+        <v>1.766</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0001</v>
+        <v>0.0036</v>
       </c>
     </row>
     <row r="43">
@@ -3652,19 +3652,19 @@
         <v>148</v>
       </c>
       <c r="B43" t="n">
-        <v>1.685</v>
+        <v>1.738</v>
       </c>
       <c r="C43" t="n">
-        <v>1.698</v>
+        <v>1.727</v>
       </c>
       <c r="D43" t="n">
-        <v>0.014</v>
+        <v>-0.011</v>
       </c>
       <c r="E43" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="44">
@@ -3672,19 +3672,19 @@
         <v>149</v>
       </c>
       <c r="B44" t="n">
-        <v>1.734</v>
+        <v>1.685</v>
       </c>
       <c r="C44" t="n">
-        <v>1.648</v>
+        <v>1.702</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.086</v>
+        <v>0.017</v>
       </c>
       <c r="E44" t="n">
-        <v>0.086</v>
+        <v>0.017</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0073</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="45">
@@ -3692,19 +3692,19 @@
         <v>150</v>
       </c>
       <c r="B45" t="n">
-        <v>2.092</v>
+        <v>1.734</v>
       </c>
       <c r="C45" t="n">
-        <v>1.821</v>
+        <v>1.649</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.271</v>
+        <v>-0.085</v>
       </c>
       <c r="E45" t="n">
-        <v>0.271</v>
+        <v>0.085</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0735</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="46">
@@ -3712,19 +3712,19 @@
         <v>151</v>
       </c>
       <c r="B46" t="n">
-        <v>2.32</v>
+        <v>2.092</v>
       </c>
       <c r="C46" t="n">
-        <v>2.126</v>
+        <v>1.823</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.193</v>
+        <v>-0.27</v>
       </c>
       <c r="E46" t="n">
-        <v>0.193</v>
+        <v>0.27</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0374</v>
+        <v>0.0728</v>
       </c>
     </row>
     <row r="47">
@@ -3732,19 +3732,19 @@
         <v>152</v>
       </c>
       <c r="B47" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="C47" t="n">
-        <v>2.314</v>
+        <v>2.126</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.286</v>
+        <v>-0.193</v>
       </c>
       <c r="E47" t="n">
-        <v>0.286</v>
+        <v>0.193</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0816</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="48">
@@ -3752,19 +3752,19 @@
         <v>153</v>
       </c>
       <c r="B48" t="n">
-        <v>2.341</v>
+        <v>2.6</v>
       </c>
       <c r="C48" t="n">
-        <v>2.24</v>
+        <v>2.313</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.101</v>
+        <v>-0.287</v>
       </c>
       <c r="E48" t="n">
-        <v>0.101</v>
+        <v>0.287</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0102</v>
+        <v>0.0821</v>
       </c>
     </row>
     <row r="49">
@@ -3772,19 +3772,19 @@
         <v>154</v>
       </c>
       <c r="B49" t="n">
-        <v>1.494</v>
+        <v>2.341</v>
       </c>
       <c r="C49" t="n">
-        <v>1.448</v>
+        <v>2.245</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.046</v>
+        <v>-0.096</v>
       </c>
       <c r="E49" t="n">
-        <v>0.046</v>
+        <v>0.096</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0021</v>
+        <v>0.0093</v>
       </c>
     </row>
     <row r="50">
@@ -3792,19 +3792,19 @@
         <v>155</v>
       </c>
       <c r="B50" t="n">
-        <v>0.313</v>
+        <v>1.494</v>
       </c>
       <c r="C50" t="n">
-        <v>0.127</v>
+        <v>1.453</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.186</v>
+        <v>-0.041</v>
       </c>
       <c r="E50" t="n">
-        <v>0.186</v>
+        <v>0.041</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0347</v>
+        <v>0.0017</v>
       </c>
     </row>
     <row r="51">
@@ -3812,19 +3812,19 @@
         <v>156</v>
       </c>
       <c r="B51" t="n">
-        <v>0.198</v>
+        <v>0.313</v>
       </c>
       <c r="C51" t="n">
-        <v>1.204</v>
+        <v>0.149</v>
       </c>
       <c r="D51" t="n">
-        <v>1.006</v>
+        <v>-0.164</v>
       </c>
       <c r="E51" t="n">
-        <v>1.006</v>
+        <v>0.164</v>
       </c>
       <c r="F51" t="n">
-        <v>1.0123</v>
+        <v>0.0268</v>
       </c>
     </row>
     <row r="52">
@@ -3832,19 +3832,19 @@
         <v>157</v>
       </c>
       <c r="B52" t="n">
-        <v>0.717</v>
+        <v>0.198</v>
       </c>
       <c r="C52" t="n">
-        <v>0.883</v>
+        <v>1.19</v>
       </c>
       <c r="D52" t="n">
-        <v>0.167</v>
+        <v>0.991</v>
       </c>
       <c r="E52" t="n">
-        <v>0.167</v>
+        <v>0.991</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0278</v>
+        <v>0.9828</v>
       </c>
     </row>
     <row r="53">
@@ -3852,19 +3852,19 @@
         <v>158</v>
       </c>
       <c r="B53" t="n">
-        <v>0.997</v>
+        <v>0.717</v>
       </c>
       <c r="C53" t="n">
-        <v>1.179</v>
+        <v>0.875</v>
       </c>
       <c r="D53" t="n">
-        <v>0.182</v>
+        <v>0.158</v>
       </c>
       <c r="E53" t="n">
-        <v>0.182</v>
+        <v>0.158</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0332</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="54">
@@ -3872,19 +3872,19 @@
         <v>159</v>
       </c>
       <c r="B54" t="n">
-        <v>1.281</v>
+        <v>0.997</v>
       </c>
       <c r="C54" t="n">
-        <v>1.24</v>
+        <v>1.175</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.041</v>
+        <v>0.178</v>
       </c>
       <c r="E54" t="n">
-        <v>0.041</v>
+        <v>0.178</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0016</v>
+        <v>0.0317</v>
       </c>
     </row>
     <row r="55">
@@ -3892,19 +3892,19 @@
         <v>160</v>
       </c>
       <c r="B55" t="n">
-        <v>1.391</v>
+        <v>1.281</v>
       </c>
       <c r="C55" t="n">
-        <v>1.383</v>
+        <v>1.239</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.008</v>
+        <v>-0.042</v>
       </c>
       <c r="E55" t="n">
-        <v>0.008</v>
+        <v>0.042</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0001</v>
+        <v>0.0017</v>
       </c>
     </row>
     <row r="56">
@@ -3912,19 +3912,19 @@
         <v>161</v>
       </c>
       <c r="B56" t="n">
-        <v>1.23</v>
+        <v>1.391</v>
       </c>
       <c r="C56" t="n">
-        <v>1.504</v>
+        <v>1.382</v>
       </c>
       <c r="D56" t="n">
-        <v>0.274</v>
+        <v>-0.009</v>
       </c>
       <c r="E56" t="n">
-        <v>0.274</v>
+        <v>0.009</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0751</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="57">
@@ -3932,19 +3932,19 @@
         <v>162</v>
       </c>
       <c r="B57" t="n">
-        <v>1.176</v>
+        <v>1.23</v>
       </c>
       <c r="C57" t="n">
-        <v>1.399</v>
+        <v>1.504</v>
       </c>
       <c r="D57" t="n">
-        <v>0.223</v>
+        <v>0.274</v>
       </c>
       <c r="E57" t="n">
-        <v>0.223</v>
+        <v>0.274</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0499</v>
+        <v>0.0749</v>
       </c>
     </row>
     <row r="58">
@@ -3952,19 +3952,19 @@
         <v>163</v>
       </c>
       <c r="B58" t="n">
-        <v>1.32</v>
+        <v>1.176</v>
       </c>
       <c r="C58" t="n">
-        <v>1.423</v>
+        <v>1.401</v>
       </c>
       <c r="D58" t="n">
-        <v>0.103</v>
+        <v>0.225</v>
       </c>
       <c r="E58" t="n">
-        <v>0.103</v>
+        <v>0.225</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0105</v>
+        <v>0.0506</v>
       </c>
     </row>
     <row r="59">
@@ -3972,19 +3972,19 @@
         <v>164</v>
       </c>
       <c r="B59" t="n">
-        <v>1.355</v>
+        <v>1.32</v>
       </c>
       <c r="C59" t="n">
-        <v>1.843</v>
+        <v>1.424</v>
       </c>
       <c r="D59" t="n">
-        <v>0.487</v>
+        <v>0.104</v>
       </c>
       <c r="E59" t="n">
-        <v>0.487</v>
+        <v>0.104</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2374</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="60">
@@ -3992,19 +3992,19 @@
         <v>165</v>
       </c>
       <c r="B60" t="n">
-        <v>1.668</v>
+        <v>1.355</v>
       </c>
       <c r="C60" t="n">
-        <v>1.842</v>
+        <v>1.846</v>
       </c>
       <c r="D60" t="n">
-        <v>0.174</v>
+        <v>0.49</v>
       </c>
       <c r="E60" t="n">
-        <v>0.174</v>
+        <v>0.49</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0304</v>
+        <v>0.2403</v>
       </c>
     </row>
     <row r="61">
@@ -4012,19 +4012,19 @@
         <v>166</v>
       </c>
       <c r="B61" t="n">
-        <v>2.624</v>
+        <v>1.668</v>
       </c>
       <c r="C61" t="n">
-        <v>2.341</v>
+        <v>1.848</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.283</v>
+        <v>0.181</v>
       </c>
       <c r="E61" t="n">
-        <v>0.283</v>
+        <v>0.181</v>
       </c>
       <c r="F61" t="n">
-        <v>0.08</v>
+        <v>0.0327</v>
       </c>
     </row>
     <row r="62">
@@ -4032,19 +4032,19 @@
         <v>167</v>
       </c>
       <c r="B62" t="n">
-        <v>4.137</v>
+        <v>2.624</v>
       </c>
       <c r="C62" t="n">
-        <v>2.844</v>
+        <v>2.333</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.293</v>
+        <v>-0.29</v>
       </c>
       <c r="E62" t="n">
-        <v>1.293</v>
+        <v>0.29</v>
       </c>
       <c r="F62" t="n">
-        <v>1.6718</v>
+        <v>0.0844</v>
       </c>
     </row>
     <row r="63">
@@ -4052,19 +4052,19 @@
         <v>168</v>
       </c>
       <c r="B63" t="n">
-        <v>4.926</v>
+        <v>4.137</v>
       </c>
       <c r="C63" t="n">
-        <v>4.617</v>
+        <v>2.842</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.309</v>
+        <v>-1.295</v>
       </c>
       <c r="E63" t="n">
-        <v>0.309</v>
+        <v>1.295</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0956</v>
+        <v>1.6768</v>
       </c>
     </row>
     <row r="64">
@@ -4072,19 +4072,19 @@
         <v>169</v>
       </c>
       <c r="B64" t="n">
-        <v>5.317</v>
+        <v>4.926</v>
       </c>
       <c r="C64" t="n">
-        <v>5.2</v>
+        <v>4.62</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.117</v>
+        <v>-0.306</v>
       </c>
       <c r="E64" t="n">
-        <v>0.117</v>
+        <v>0.306</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0137</v>
+        <v>0.0939</v>
       </c>
     </row>
     <row r="65">
@@ -4092,19 +4092,19 @@
         <v>170</v>
       </c>
       <c r="B65" t="n">
-        <v>5.269</v>
+        <v>5.317</v>
       </c>
       <c r="C65" t="n">
-        <v>5.215</v>
+        <v>5.202</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.054</v>
+        <v>-0.116</v>
       </c>
       <c r="E65" t="n">
-        <v>0.054</v>
+        <v>0.116</v>
       </c>
       <c r="F65" t="n">
-        <v>0.003</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="66">
@@ -4112,19 +4112,19 @@
         <v>171</v>
       </c>
       <c r="B66" t="n">
-        <v>5.181</v>
+        <v>5.269</v>
       </c>
       <c r="C66" t="n">
-        <v>5.213</v>
+        <v>5.218</v>
       </c>
       <c r="D66" t="n">
-        <v>0.032</v>
+        <v>-0.051</v>
       </c>
       <c r="E66" t="n">
-        <v>0.032</v>
+        <v>0.051</v>
       </c>
       <c r="F66" t="n">
-        <v>0.001</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="67">
@@ -4132,19 +4132,19 @@
         <v>172</v>
       </c>
       <c r="B67" t="n">
-        <v>5.364</v>
+        <v>5.181</v>
       </c>
       <c r="C67" t="n">
-        <v>5.214</v>
+        <v>5.204</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.149</v>
+        <v>0.022</v>
       </c>
       <c r="E67" t="n">
-        <v>0.149</v>
+        <v>0.022</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0222</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="68">
@@ -4152,19 +4152,19 @@
         <v>173</v>
       </c>
       <c r="B68" t="n">
-        <v>6.227</v>
+        <v>5.364</v>
       </c>
       <c r="C68" t="n">
-        <v>5.602</v>
+        <v>5.217</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.625</v>
+        <v>-0.147</v>
       </c>
       <c r="E68" t="n">
-        <v>0.625</v>
+        <v>0.147</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3904</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="69">
@@ -4172,19 +4172,19 @@
         <v>174</v>
       </c>
       <c r="B69" t="n">
-        <v>6.866</v>
+        <v>6.227</v>
       </c>
       <c r="C69" t="n">
-        <v>6.372</v>
+        <v>5.604</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.494</v>
+        <v>-0.623</v>
       </c>
       <c r="E69" t="n">
-        <v>0.494</v>
+        <v>0.623</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2439</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="70">
@@ -4192,19 +4192,19 @@
         <v>175</v>
       </c>
       <c r="B70" t="n">
-        <v>7.159</v>
+        <v>6.866</v>
       </c>
       <c r="C70" t="n">
-        <v>6.336</v>
+        <v>6.365</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.823</v>
+        <v>-0.5</v>
       </c>
       <c r="E70" t="n">
-        <v>0.823</v>
+        <v>0.5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.678</v>
+        <v>0.2503</v>
       </c>
     </row>
     <row r="71">
@@ -4212,19 +4212,19 @@
         <v>176</v>
       </c>
       <c r="B71" t="n">
-        <v>7.578</v>
+        <v>7.159</v>
       </c>
       <c r="C71" t="n">
-        <v>7.287</v>
+        <v>6.348</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.291</v>
+        <v>-0.812</v>
       </c>
       <c r="E71" t="n">
-        <v>0.291</v>
+        <v>0.812</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0849</v>
+        <v>0.6588</v>
       </c>
     </row>
     <row r="72">
@@ -4232,19 +4232,19 @@
         <v>177</v>
       </c>
       <c r="B72" t="n">
-        <v>7.949</v>
+        <v>7.578</v>
       </c>
       <c r="C72" t="n">
-        <v>7.668</v>
+        <v>7.285</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.281</v>
+        <v>-0.293</v>
       </c>
       <c r="E72" t="n">
-        <v>0.281</v>
+        <v>0.293</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0792</v>
+        <v>0.0858</v>
       </c>
     </row>
     <row r="73">
@@ -4252,19 +4252,19 @@
         <v>178</v>
       </c>
       <c r="B73" t="n">
-        <v>8.541</v>
+        <v>7.949</v>
       </c>
       <c r="C73" t="n">
-        <v>8.375</v>
+        <v>7.673</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.166</v>
+        <v>-0.277</v>
       </c>
       <c r="E73" t="n">
-        <v>0.166</v>
+        <v>0.277</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0275</v>
+        <v>0.0765</v>
       </c>
     </row>
     <row r="74">
@@ -4272,19 +4272,19 @@
         <v>179</v>
       </c>
       <c r="B74" t="n">
-        <v>8.235</v>
+        <v>8.541</v>
       </c>
       <c r="C74" t="n">
-        <v>8.333</v>
+        <v>8.382</v>
       </c>
       <c r="D74" t="n">
-        <v>0.097</v>
+        <v>-0.159</v>
       </c>
       <c r="E74" t="n">
-        <v>0.097</v>
+        <v>0.159</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0095</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="75">
@@ -4292,19 +4292,19 @@
         <v>180</v>
       </c>
       <c r="B75" t="n">
-        <v>8.53</v>
+        <v>8.235</v>
       </c>
       <c r="C75" t="n">
-        <v>8.347</v>
+        <v>8.327</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.183</v>
+        <v>0.092</v>
       </c>
       <c r="E75" t="n">
-        <v>0.183</v>
+        <v>0.092</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0335</v>
+        <v>0.0085</v>
       </c>
     </row>
     <row r="76">
@@ -4312,19 +4312,19 @@
         <v>181</v>
       </c>
       <c r="B76" t="n">
-        <v>8.999</v>
+        <v>8.53</v>
       </c>
       <c r="C76" t="n">
-        <v>8.682</v>
+        <v>8.352</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.317</v>
+        <v>-0.179</v>
       </c>
       <c r="E76" t="n">
-        <v>0.317</v>
+        <v>0.179</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1005</v>
+        <v>0.0319</v>
       </c>
     </row>
     <row r="77">
@@ -4332,19 +4332,19 @@
         <v>182</v>
       </c>
       <c r="B77" t="n">
-        <v>8.448</v>
+        <v>8.999</v>
       </c>
       <c r="C77" t="n">
-        <v>7.926</v>
+        <v>8.685</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.522</v>
+        <v>-0.314</v>
       </c>
       <c r="E77" t="n">
-        <v>0.522</v>
+        <v>0.314</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2723</v>
+        <v>0.0986</v>
       </c>
     </row>
     <row r="78">
@@ -4352,19 +4352,19 @@
         <v>183</v>
       </c>
       <c r="B78" t="n">
-        <v>8.216</v>
+        <v>8.448</v>
       </c>
       <c r="C78" t="n">
-        <v>7.76</v>
+        <v>7.928</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.456</v>
+        <v>-0.52</v>
       </c>
       <c r="E78" t="n">
-        <v>0.456</v>
+        <v>0.52</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2082</v>
+        <v>0.2701</v>
       </c>
     </row>
     <row r="79">
@@ -4372,19 +4372,19 @@
         <v>184</v>
       </c>
       <c r="B79" t="n">
-        <v>8.206</v>
+        <v>8.216</v>
       </c>
       <c r="C79" t="n">
-        <v>7.696</v>
+        <v>7.745</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.509</v>
+        <v>-0.471</v>
       </c>
       <c r="E79" t="n">
-        <v>0.509</v>
+        <v>0.471</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2594</v>
+        <v>0.2222</v>
       </c>
     </row>
     <row r="80">
@@ -4392,19 +4392,19 @@
         <v>185</v>
       </c>
       <c r="B80" t="n">
-        <v>7.757</v>
+        <v>8.206</v>
       </c>
       <c r="C80" t="n">
-        <v>7.6</v>
+        <v>7.699</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.157</v>
+        <v>-0.507</v>
       </c>
       <c r="E80" t="n">
-        <v>0.157</v>
+        <v>0.507</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0246</v>
+        <v>0.2572</v>
       </c>
     </row>
     <row r="81">
@@ -4412,19 +4412,19 @@
         <v>186</v>
       </c>
       <c r="B81" t="n">
-        <v>7.131</v>
+        <v>7.757</v>
       </c>
       <c r="C81" t="n">
-        <v>7.193</v>
+        <v>7.592</v>
       </c>
       <c r="D81" t="n">
-        <v>0.061</v>
+        <v>-0.166</v>
       </c>
       <c r="E81" t="n">
-        <v>0.061</v>
+        <v>0.166</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0038</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="82">
@@ -4432,19 +4432,19 @@
         <v>187</v>
       </c>
       <c r="B82" t="n">
-        <v>6.411</v>
+        <v>7.131</v>
       </c>
       <c r="C82" t="n">
-        <v>6.475</v>
+        <v>7.198</v>
       </c>
       <c r="D82" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="E82" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0041</v>
+        <v>0.0044</v>
       </c>
     </row>
     <row r="83">
@@ -4452,19 +4452,19 @@
         <v>188</v>
       </c>
       <c r="B83" t="n">
-        <v>6.34</v>
+        <v>6.411</v>
       </c>
       <c r="C83" t="n">
-        <v>6.368</v>
+        <v>6.478</v>
       </c>
       <c r="D83" t="n">
-        <v>0.028</v>
+        <v>0.067</v>
       </c>
       <c r="E83" t="n">
-        <v>0.028</v>
+        <v>0.067</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0008</v>
+        <v>0.0045</v>
       </c>
     </row>
     <row r="84">
@@ -4472,19 +4472,19 @@
         <v>189</v>
       </c>
       <c r="B84" t="n">
-        <v>5.958</v>
+        <v>6.34</v>
       </c>
       <c r="C84" t="n">
-        <v>5.948</v>
+        <v>6.373</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.009</v>
+        <v>0.033</v>
       </c>
       <c r="E84" t="n">
-        <v>0.009</v>
+        <v>0.033</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0001</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="85">
@@ -4492,19 +4492,19 @@
         <v>190</v>
       </c>
       <c r="B85" t="n">
-        <v>4.931</v>
+        <v>5.958</v>
       </c>
       <c r="C85" t="n">
-        <v>5.517</v>
+        <v>5.95</v>
       </c>
       <c r="D85" t="n">
-        <v>0.585</v>
+        <v>-0.008</v>
       </c>
       <c r="E85" t="n">
-        <v>0.585</v>
+        <v>0.008</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3425</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="86">
@@ -4512,19 +4512,19 @@
         <v>191</v>
       </c>
       <c r="B86" t="n">
-        <v>4.947</v>
+        <v>4.931</v>
       </c>
       <c r="C86" t="n">
-        <v>4.855</v>
+        <v>5.528</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.092</v>
+        <v>0.597</v>
       </c>
       <c r="E86" t="n">
-        <v>0.092</v>
+        <v>0.597</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0085</v>
+        <v>0.3559</v>
       </c>
     </row>
     <row r="87">
@@ -4532,19 +4532,19 @@
         <v>192</v>
       </c>
       <c r="B87" t="n">
-        <v>4.125</v>
+        <v>4.947</v>
       </c>
       <c r="C87" t="n">
-        <v>4.513</v>
+        <v>4.844</v>
       </c>
       <c r="D87" t="n">
-        <v>0.387</v>
+        <v>-0.103</v>
       </c>
       <c r="E87" t="n">
-        <v>0.387</v>
+        <v>0.103</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1502</v>
+        <v>0.0106</v>
       </c>
     </row>
     <row r="88">
@@ -4552,19 +4552,19 @@
         <v>193</v>
       </c>
       <c r="B88" t="n">
-        <v>3.059</v>
+        <v>4.125</v>
       </c>
       <c r="C88" t="n">
-        <v>3.961</v>
+        <v>4.518</v>
       </c>
       <c r="D88" t="n">
-        <v>0.902</v>
+        <v>0.392</v>
       </c>
       <c r="E88" t="n">
-        <v>0.902</v>
+        <v>0.392</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8134</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="89">
@@ -4572,19 +4572,19 @@
         <v>194</v>
       </c>
       <c r="B89" t="n">
-        <v>3.28</v>
+        <v>3.059</v>
       </c>
       <c r="C89" t="n">
-        <v>3.006</v>
+        <v>3.961</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.275</v>
+        <v>0.902</v>
       </c>
       <c r="E89" t="n">
-        <v>0.275</v>
+        <v>0.902</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0754</v>
+        <v>0.8139</v>
       </c>
     </row>
     <row r="90">
@@ -4592,19 +4592,19 @@
         <v>195</v>
       </c>
       <c r="B90" t="n">
-        <v>3.719</v>
+        <v>3.28</v>
       </c>
       <c r="C90" t="n">
-        <v>3.49</v>
+        <v>3.004</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.229</v>
+        <v>-0.276</v>
       </c>
       <c r="E90" t="n">
-        <v>0.229</v>
+        <v>0.276</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0523</v>
+        <v>0.0763</v>
       </c>
     </row>
     <row r="91">
@@ -4612,19 +4612,19 @@
         <v>196</v>
       </c>
       <c r="B91" t="n">
-        <v>3.695</v>
+        <v>3.719</v>
       </c>
       <c r="C91" t="n">
-        <v>3.76</v>
+        <v>3.489</v>
       </c>
       <c r="D91" t="n">
-        <v>0.065</v>
+        <v>-0.229</v>
       </c>
       <c r="E91" t="n">
-        <v>0.065</v>
+        <v>0.229</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0043</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="92">
@@ -4632,19 +4632,19 @@
         <v>197</v>
       </c>
       <c r="B92" t="n">
-        <v>3.247</v>
+        <v>3.695</v>
       </c>
       <c r="C92" t="n">
-        <v>3.383</v>
+        <v>3.758</v>
       </c>
       <c r="D92" t="n">
-        <v>0.137</v>
+        <v>0.063</v>
       </c>
       <c r="E92" t="n">
-        <v>0.137</v>
+        <v>0.063</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0187</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="93">
@@ -4652,19 +4652,19 @@
         <v>198</v>
       </c>
       <c r="B93" t="n">
-        <v>3.14</v>
+        <v>3.247</v>
       </c>
       <c r="C93" t="n">
-        <v>3.032</v>
+        <v>3.377</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.108</v>
+        <v>0.131</v>
       </c>
       <c r="E93" t="n">
-        <v>0.108</v>
+        <v>0.131</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0116</v>
+        <v>0.0171</v>
       </c>
     </row>
     <row r="94">
@@ -4672,19 +4672,19 @@
         <v>199</v>
       </c>
       <c r="B94" t="n">
-        <v>3.322</v>
+        <v>3.14</v>
       </c>
       <c r="C94" t="n">
-        <v>2.851</v>
+        <v>3.035</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.471</v>
+        <v>-0.105</v>
       </c>
       <c r="E94" t="n">
-        <v>0.471</v>
+        <v>0.105</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2221</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="95">
@@ -4692,19 +4692,19 @@
         <v>200</v>
       </c>
       <c r="B95" t="n">
-        <v>3.108</v>
+        <v>3.322</v>
       </c>
       <c r="C95" t="n">
-        <v>3.29</v>
+        <v>2.861</v>
       </c>
       <c r="D95" t="n">
-        <v>0.182</v>
+        <v>-0.461</v>
       </c>
       <c r="E95" t="n">
-        <v>0.182</v>
+        <v>0.461</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0332</v>
+        <v>0.2124</v>
       </c>
     </row>
     <row r="96">
@@ -4712,19 +4712,19 @@
         <v>201</v>
       </c>
       <c r="B96" t="n">
-        <v>3.166</v>
+        <v>3.108</v>
       </c>
       <c r="C96" t="n">
-        <v>3.314</v>
+        <v>3.292</v>
       </c>
       <c r="D96" t="n">
-        <v>0.147</v>
+        <v>0.184</v>
       </c>
       <c r="E96" t="n">
-        <v>0.147</v>
+        <v>0.184</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0217</v>
+        <v>0.0337</v>
       </c>
     </row>
     <row r="97">
@@ -4732,19 +4732,19 @@
         <v>202</v>
       </c>
       <c r="B97" t="n">
-        <v>3.469</v>
+        <v>3.166</v>
       </c>
       <c r="C97" t="n">
-        <v>3.17</v>
+        <v>3.316</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.299</v>
+        <v>0.15</v>
       </c>
       <c r="E97" t="n">
-        <v>0.299</v>
+        <v>0.15</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0893</v>
+        <v>0.0224</v>
       </c>
     </row>
     <row r="98">
@@ -4752,19 +4752,19 @@
         <v>203</v>
       </c>
       <c r="B98" t="n">
-        <v>3.354</v>
+        <v>3.469</v>
       </c>
       <c r="C98" t="n">
-        <v>3.519</v>
+        <v>3.179</v>
       </c>
       <c r="D98" t="n">
-        <v>0.165</v>
+        <v>-0.29</v>
       </c>
       <c r="E98" t="n">
-        <v>0.165</v>
+        <v>0.29</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0273</v>
+        <v>0.0841</v>
       </c>
     </row>
     <row r="99">
@@ -4772,19 +4772,19 @@
         <v>204</v>
       </c>
       <c r="B99" t="n">
-        <v>3.239</v>
+        <v>3.354</v>
       </c>
       <c r="C99" t="n">
-        <v>3.183</v>
+        <v>3.508</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.056</v>
+        <v>0.154</v>
       </c>
       <c r="E99" t="n">
-        <v>0.056</v>
+        <v>0.154</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0031</v>
+        <v>0.0237</v>
       </c>
     </row>
     <row r="100">
@@ -4792,19 +4792,19 @@
         <v>205</v>
       </c>
       <c r="B100" t="n">
-        <v>2.97</v>
+        <v>3.239</v>
       </c>
       <c r="C100" t="n">
-        <v>3.161</v>
+        <v>3.192</v>
       </c>
       <c r="D100" t="n">
-        <v>0.191</v>
+        <v>-0.047</v>
       </c>
       <c r="E100" t="n">
-        <v>0.191</v>
+        <v>0.047</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0366</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="101">
@@ -4812,19 +4812,19 @@
         <v>206</v>
       </c>
       <c r="B101" t="n">
-        <v>2.938</v>
+        <v>2.97</v>
       </c>
       <c r="C101" t="n">
-        <v>3.066</v>
+        <v>3.153</v>
       </c>
       <c r="D101" t="n">
-        <v>0.128</v>
+        <v>0.183</v>
       </c>
       <c r="E101" t="n">
-        <v>0.128</v>
+        <v>0.183</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0163</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="102">
@@ -4832,19 +4832,19 @@
         <v>207</v>
       </c>
       <c r="B102" t="n">
-        <v>2.611</v>
+        <v>2.938</v>
       </c>
       <c r="C102" t="n">
-        <v>2.699</v>
+        <v>3.062</v>
       </c>
       <c r="D102" t="n">
-        <v>0.088</v>
+        <v>0.123</v>
       </c>
       <c r="E102" t="n">
-        <v>0.088</v>
+        <v>0.123</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0078</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="103">
@@ -4852,19 +4852,19 @@
         <v>208</v>
       </c>
       <c r="B103" t="n">
-        <v>2.433</v>
+        <v>2.611</v>
       </c>
       <c r="C103" t="n">
-        <v>2.454</v>
+        <v>2.693</v>
       </c>
       <c r="D103" t="n">
-        <v>0.021</v>
+        <v>0.082</v>
       </c>
       <c r="E103" t="n">
-        <v>0.021</v>
+        <v>0.082</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0004</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="104">
@@ -4872,19 +4872,19 @@
         <v>209</v>
       </c>
       <c r="B104" t="n">
-        <v>2.571</v>
+        <v>2.433</v>
       </c>
       <c r="C104" t="n">
-        <v>2.415</v>
+        <v>2.441</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.156</v>
+        <v>0.008</v>
       </c>
       <c r="E104" t="n">
-        <v>0.156</v>
+        <v>0.008</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0243</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="105">
@@ -4892,19 +4892,19 @@
         <v>210</v>
       </c>
       <c r="B105" t="n">
-        <v>2.714</v>
+        <v>2.571</v>
       </c>
       <c r="C105" t="n">
-        <v>2.539</v>
+        <v>2.418</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.175</v>
+        <v>-0.154</v>
       </c>
       <c r="E105" t="n">
-        <v>0.175</v>
+        <v>0.154</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0307</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="106">
@@ -4912,19 +4912,19 @@
         <v>211</v>
       </c>
       <c r="B106" t="n">
-        <v>2.872</v>
+        <v>2.714</v>
       </c>
       <c r="C106" t="n">
-        <v>2.781</v>
+        <v>2.545</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.091</v>
+        <v>-0.17</v>
       </c>
       <c r="E106" t="n">
-        <v>0.091</v>
+        <v>0.17</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0084</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="107">
@@ -4932,19 +4932,19 @@
         <v>212</v>
       </c>
       <c r="B107" t="n">
-        <v>2.999</v>
+        <v>2.872</v>
       </c>
       <c r="C107" t="n">
-        <v>3.162</v>
+        <v>2.776</v>
       </c>
       <c r="D107" t="n">
-        <v>0.163</v>
+        <v>-0.096</v>
       </c>
       <c r="E107" t="n">
-        <v>0.163</v>
+        <v>0.096</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0265</v>
+        <v>0.0093</v>
       </c>
     </row>
     <row r="108">
@@ -4952,19 +4952,19 @@
         <v>213</v>
       </c>
       <c r="B108" t="n">
-        <v>2.814</v>
+        <v>2.999</v>
       </c>
       <c r="C108" t="n">
-        <v>3.027</v>
+        <v>3.177</v>
       </c>
       <c r="D108" t="n">
-        <v>0.212</v>
+        <v>0.178</v>
       </c>
       <c r="E108" t="n">
-        <v>0.212</v>
+        <v>0.178</v>
       </c>
       <c r="F108" t="n">
-        <v>0.045</v>
+        <v>0.0316</v>
       </c>
     </row>
     <row r="109">
@@ -4972,19 +4972,19 @@
         <v>214</v>
       </c>
       <c r="B109" t="n">
-        <v>2.406</v>
+        <v>2.814</v>
       </c>
       <c r="C109" t="n">
-        <v>2.844</v>
+        <v>3.026</v>
       </c>
       <c r="D109" t="n">
-        <v>0.439</v>
+        <v>0.211</v>
       </c>
       <c r="E109" t="n">
-        <v>0.439</v>
+        <v>0.211</v>
       </c>
       <c r="F109" t="n">
-        <v>0.1925</v>
+        <v>0.0447</v>
       </c>
     </row>
     <row r="110">
@@ -4992,19 +4992,19 @@
         <v>215</v>
       </c>
       <c r="B110" t="n">
-        <v>2.334</v>
+        <v>2.406</v>
       </c>
       <c r="C110" t="n">
-        <v>2.043</v>
+        <v>2.844</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.291</v>
+        <v>0.438</v>
       </c>
       <c r="E110" t="n">
-        <v>0.291</v>
+        <v>0.438</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0847</v>
+        <v>0.1922</v>
       </c>
     </row>
     <row r="111">
@@ -5012,19 +5012,19 @@
         <v>216</v>
       </c>
       <c r="B111" t="n">
-        <v>2.376</v>
+        <v>2.334</v>
       </c>
       <c r="C111" t="n">
-        <v>2.275</v>
+        <v>2.043</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.101</v>
+        <v>-0.291</v>
       </c>
       <c r="E111" t="n">
-        <v>0.101</v>
+        <v>0.291</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0102</v>
+        <v>0.0847</v>
       </c>
     </row>
     <row r="112">
@@ -5032,19 +5032,19 @@
         <v>217</v>
       </c>
       <c r="B112" t="n">
-        <v>2.673</v>
+        <v>2.376</v>
       </c>
       <c r="C112" t="n">
-        <v>2.332</v>
+        <v>2.296</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.341</v>
+        <v>-0.08</v>
       </c>
       <c r="E112" t="n">
-        <v>0.341</v>
+        <v>0.08</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1162</v>
+        <v>0.0064</v>
       </c>
     </row>
     <row r="113">
@@ -5052,19 +5052,19 @@
         <v>218</v>
       </c>
       <c r="B113" t="n">
-        <v>2.732</v>
+        <v>2.673</v>
       </c>
       <c r="C113" t="n">
-        <v>2.792</v>
+        <v>2.315</v>
       </c>
       <c r="D113" t="n">
-        <v>0.06</v>
+        <v>-0.357</v>
       </c>
       <c r="E113" t="n">
-        <v>0.06</v>
+        <v>0.357</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0036</v>
+        <v>0.1277</v>
       </c>
     </row>
     <row r="114">
@@ -5072,19 +5072,19 @@
         <v>219</v>
       </c>
       <c r="B114" t="n">
-        <v>2.939</v>
+        <v>2.732</v>
       </c>
       <c r="C114" t="n">
-        <v>2.625</v>
+        <v>2.788</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.315</v>
+        <v>0.056</v>
       </c>
       <c r="E114" t="n">
-        <v>0.315</v>
+        <v>0.056</v>
       </c>
       <c r="F114" t="n">
-        <v>0.099</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="115">
@@ -5092,19 +5092,19 @@
         <v>6</v>
       </c>
       <c r="B115" t="n">
-        <v>3.023</v>
+        <v>2.939</v>
       </c>
       <c r="C115" t="n">
-        <v>2.853</v>
+        <v>2.622</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.17</v>
+        <v>-0.317</v>
       </c>
       <c r="E115" t="n">
-        <v>0.17</v>
+        <v>0.317</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0289</v>
+        <v>0.1007</v>
       </c>
     </row>
   </sheetData>
@@ -5137,10 +5137,10 @@
         <v>100</v>
       </c>
       <c r="B2" t="n">
-        <v>1.0815</v>
+        <v>1.08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0815</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="3">
@@ -5148,10 +5148,10 @@
         <v>49</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1587</v>
+        <v>0.159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1587</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="4">
@@ -5159,32 +5159,32 @@
         <v>39</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0517</v>
+        <v>0.0502</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0517</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0346</v>
+        <v>0.0368</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0346</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B6" t="n">
-        <v>0.034</v>
+        <v>0.0351</v>
       </c>
       <c r="C6" t="n">
-        <v>0.034</v>
+        <v>0.0351</v>
       </c>
     </row>
     <row r="7">
@@ -5192,10 +5192,10 @@
         <v>65</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0279</v>
+        <v>0.0287</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0279</v>
+        <v>0.0287</v>
       </c>
     </row>
     <row r="8">
@@ -5203,10 +5203,10 @@
         <v>27</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0255</v>
+        <v>0.0244</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0255</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="9">
@@ -5214,10 +5214,10 @@
         <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0228</v>
+        <v>-0.023</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0228</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="10">
@@ -5225,10 +5225,10 @@
         <v>37</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0146</v>
+        <v>-0.0139</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0146</v>
+        <v>0.0139</v>
       </c>
     </row>
     <row r="11">
@@ -5236,10 +5236,10 @@
         <v>67</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0017</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="12">
@@ -5247,10 +5247,10 @@
         <v>25</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.001</v>
+        <v>-0.0007</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001</v>
+        <v>0.0007</v>
       </c>
     </row>
   </sheetData>
